--- a/tools/importer/reports/import-product-page.report.xlsx
+++ b/tools/importer/reports/import-product-page.report.xlsx
@@ -466,13 +466,13 @@
     <t>products/wireless-plans.report.json</t>
   </si>
   <si>
-    <t>["hero-banner","cards-product","cards-product","cards-product","cards-value","cards-value","hero-dark","hero-dark","hero-dark","columns-offer","accordion-faq"]</t>
+    <t>["hero-banner","cards-product","cards-product","cards-product","cards-value","cards-value","hero-dark","hero-dark","hero-dark","columns-offer","accordion-faq","plan-comparison"]</t>
   </si>
   <si>
     <t>products/wireless-plans</t>
   </si>
   <si>
-    <t>2026-03-02T13:40:12.511Z</t>
+    <t>2026-03-02T14:53:49.922Z</t>
   </si>
   <si>
     <t>Business Cell Phone Plans | AT&amp;T Business Wireless &amp; Mobile</t>

--- a/tools/importer/reports/import-product-page.report.xlsx
+++ b/tools/importer/reports/import-product-page.report.xlsx
@@ -472,7 +472,7 @@
     <t>products/wireless-plans</t>
   </si>
   <si>
-    <t>2026-03-02T14:53:49.922Z</t>
+    <t>2026-03-02T15:52:53.367Z</t>
   </si>
   <si>
     <t>Business Cell Phone Plans | AT&amp;T Business Wireless &amp; Mobile</t>
